--- a/delivery_performance_dataset project.xlsx
+++ b/delivery_performance_dataset project.xlsx
@@ -5,20 +5,22 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\royvi\Downloads\Anudip\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\royvi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDE58BD5-F169-4C33-98F4-8A1739B85FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58E1AA68-146D-4204-ADBD-7C617785D1F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7506515-4838-468D-B874-5EBF127DE81C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{B7506515-4838-468D-B874-5EBF127DE81C}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
-    <sheet name="delivery_performance_dataset" sheetId="1" r:id="rId2"/>
+    <sheet name="5chartss" sheetId="2" r:id="rId1"/>
+    <sheet name="5charts" sheetId="5" r:id="rId2"/>
+    <sheet name="delivery_performance_dataset" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId3"/>
+    <pivotCache cacheId="0" r:id="rId4"/>
+    <pivotCache cacheId="16" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -35,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="45">
   <si>
     <t>Order_ID</t>
   </si>
@@ -155,6 +157,21 @@
   </si>
   <si>
     <t>Delivery Partner Performance Analysis</t>
+  </si>
+  <si>
+    <t>(blank)</t>
+  </si>
+  <si>
+    <t>Sum of Order_Value</t>
+  </si>
+  <si>
+    <t>Sum of Delivery_Time_Days</t>
+  </si>
+  <si>
+    <t>Average of Order_Value</t>
+  </si>
+  <si>
+    <t>Average of Customer_Rating</t>
   </si>
 </sst>
 </file>
@@ -638,13 +655,14 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -727,7 +745,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[delivery_performance_dataset project.xlsx]Sheet1!PivotTable3</c:name>
+    <c:name>[delivery_performance_dataset project.xlsx]5chartss!PivotTable3</c:name>
     <c:fmtId val="1"/>
   </c:pivotSource>
   <c:chart>
@@ -857,7 +875,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$E$3</c:f>
+              <c:f>'5chartss'!$E$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -878,7 +896,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$D$4:$D$8</c:f>
+              <c:f>'5chartss'!$D$4:$D$8</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
@@ -898,7 +916,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$E$4:$E$8</c:f>
+              <c:f>'5chartss'!$E$4:$E$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -1142,6 +1160,432 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[delivery_performance_dataset project.xlsx]5charts!PivotTable8</c:name>
+    <c:fmtId val="1"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-IN" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+              <a:t>Delivery Partner vs Customer Rating</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'5charts'!$B$12</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'5charts'!$A$13:$A$17</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>BlueDart</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Delhivery</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>DHL</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>(blank)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'5charts'!$B$13:$B$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.8571428571428572</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.95</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-FFF2-47BC-9255-8FF7FD11E841}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="1582579728"/>
+        <c:axId val="1582606608"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1582579728"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1582606608"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1582606608"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1582579728"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
@@ -1156,7 +1600,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[delivery_performance_dataset project.xlsx]Sheet1!PivotTable4</c:name>
+    <c:name>[delivery_performance_dataset project.xlsx]5chartss!PivotTable4</c:name>
     <c:fmtId val="1"/>
   </c:pivotSource>
   <c:chart>
@@ -1328,7 +1772,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$H$4</c:f>
+              <c:f>'5chartss'!$H$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1399,7 +1843,7 @@
           </c:dPt>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$G$5:$G$8</c:f>
+              <c:f>'5chartss'!$G$5:$G$8</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -1416,7 +1860,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$H$5:$H$8</c:f>
+              <c:f>'5chartss'!$H$5:$H$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
@@ -1562,7 +2006,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[delivery_performance_dataset project.xlsx]Sheet1!PivotTable6</c:name>
+    <c:name>[delivery_performance_dataset project.xlsx]5chartss!PivotTable6</c:name>
     <c:fmtId val="19"/>
   </c:pivotSource>
   <c:chart>
@@ -1692,7 +2136,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$E$13</c:f>
+              <c:f>'5chartss'!$E$13</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1713,7 +2157,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$D$14:$D$17</c:f>
+              <c:f>'5chartss'!$D$14:$D$17</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -1730,7 +2174,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$E$14:$E$17</c:f>
+              <c:f>'5chartss'!$E$14:$E$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
@@ -1757,7 +2201,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$F$13</c:f>
+              <c:f>'5chartss'!$F$13</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1778,7 +2222,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$D$14:$D$17</c:f>
+              <c:f>'5chartss'!$D$14:$D$17</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -1795,7 +2239,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$F$14:$F$17</c:f>
+              <c:f>'5chartss'!$F$14:$F$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
@@ -2049,7 +2493,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[delivery_performance_dataset project.xlsx]Sheet1!PivotTable7</c:name>
+    <c:name>[delivery_performance_dataset project.xlsx]5chartss!PivotTable7</c:name>
     <c:fmtId val="2"/>
   </c:pivotSource>
   <c:chart>
@@ -2249,7 +2693,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$I$14</c:f>
+              <c:f>'5chartss'!$I$14</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2360,7 +2804,7 @@
           </c:dPt>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$H$15:$H$20</c:f>
+              <c:f>'5chartss'!$H$15:$H$20</c:f>
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
@@ -2383,7 +2827,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$I$15:$I$20</c:f>
+              <c:f>'5chartss'!$I$15:$I$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -2536,7 +2980,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[delivery_performance_dataset project.xlsx]Sheet1!PivotTable1</c:name>
+    <c:name>[delivery_performance_dataset project.xlsx]5chartss!PivotTable1</c:name>
     <c:fmtId val="13"/>
   </c:pivotSource>
   <c:chart>
@@ -2676,7 +3120,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$K$4</c:f>
+              <c:f>'5chartss'!$K$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2711,7 +3155,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$J$5:$J$7</c:f>
+              <c:f>'5chartss'!$J$5:$J$7</c:f>
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
@@ -2725,7 +3169,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$K$5:$K$7</c:f>
+              <c:f>'5chartss'!$K$5:$K$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -2964,7 +3408,1697 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[delivery_performance_dataset project.xlsx]5charts!PivotTable4</c:name>
+    <c:fmtId val="8"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-IN" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+              <a:t>Revenue by City</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'5charts'!$F$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'5charts'!$E$4:$E$9</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Bangalore</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Delhi</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Mumbai</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Pune</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>(blank)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'5charts'!$F$4:$F$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>43961</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>28801</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>22314</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>44928</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3049-4AE2-98C4-51A433DA2314}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="724899024"/>
+        <c:axId val="724915824"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="724899024"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="724915824"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="724915824"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="724899024"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[delivery_performance_dataset project.xlsx]5charts!PivotTable5</c:name>
+    <c:fmtId val="3"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-IN" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+              <a:t>Delivery Time vs Status</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-IN"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'5charts'!$I$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'5charts'!$H$4:$H$8</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Cancelled</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Delayed</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Delivered</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>(blank)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'5charts'!$I$4:$I$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>86</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>113</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6B6D-40A3-83B0-09CE7700A509}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="724932624"/>
+        <c:axId val="724930704"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="724932624"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="724930704"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="724930704"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="724932624"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[delivery_performance_dataset project.xlsx]5charts!PivotTable6</c:name>
+    <c:fmtId val="1"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-IN" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+              <a:t>Payment Method Distribution</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'5charts'!$E$12</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:cat>
+            <c:strRef>
+              <c:f>'5charts'!$D$13:$D$17</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Card</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Cash</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>UPI</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>(blank)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'5charts'!$E$13:$E$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>13</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3CFF-4B5F-95DE-C291B78553E6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[delivery_performance_dataset project.xlsx]5charts!PivotTable7</c:name>
+    <c:fmtId val="4"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-IN" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+              <a:t>Product Type vs Avg Order Value</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'5charts'!$H$12</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'5charts'!$G$13:$G$17</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Clothing</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Electronics</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Groceries</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>(blank)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'5charts'!$H$13:$H$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>2872.4666666666667</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2921.8888888888887</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2607.2352941176468</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6131-4003-846F-1EC699258D81}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="1582591728"/>
+        <c:axId val="1582582128"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1582591728"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1582582128"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1582582128"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1582591728"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors10.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -3164,6 +5298,166 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors9.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
@@ -3667,8 +5961,8 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+<file path=xl/charts/style10.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -3725,7 +6019,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="1000" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
@@ -3776,13 +6070,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -3793,19 +6080,12 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="25400">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
+    <cs:fillRef idx="1"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -3843,7 +6123,7 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
+    <cs:fillRef idx="1"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -4186,8 +6466,8 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -4244,7 +6524,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
@@ -4295,6 +6575,13 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -4305,12 +6592,19 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
+    <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -4348,7 +6642,7 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
+    <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -4691,8 +6985,8 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -4749,7 +7043,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="1000" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
@@ -4800,13 +7094,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -4817,19 +7104,12 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="25400">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
+    <cs:fillRef idx="1"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -4867,7 +7147,7 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
+    <cs:fillRef idx="1"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -5210,8 +7490,8 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -5268,7 +7548,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
@@ -5319,6 +7599,525 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -5681,6 +8480,2040 @@
             <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style9.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -5878,6 +10711,191 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9022EE6E-A8EC-BF9E-C92E-1505A2577676}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>982980</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>64770</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>480060</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>64770</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{171B6FFB-36A3-00E2-728C-14705B3A409D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>762000</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>64770</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>64770</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{468E7F81-A60F-F076-B9E7-F3EAD2CBC1F5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>906780</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>144780</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>137160</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{50F0F1BD-A233-6F57-D753-8D57ED340006}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>685800</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>3810</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>3810</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2BD15B1C-E6DD-1F7E-B485-D55A1D5F688A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>769620</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>3810</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>800100</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>3810</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Chart 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7159952A-26D1-B93E-A02B-AAB0B0DBA9FC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6410,6 +11428,83 @@
           <s v="&gt;23-03-2026"/>
         </groupItems>
       </fieldGroup>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="vishakha roy" refreshedDate="46109.55481076389" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="51" xr:uid="{641E6671-4AF2-4860-A79F-4BCD32A248FF}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:L1048576" sheet="delivery_performance_dataset"/>
+  </cacheSource>
+  <cacheFields count="12">
+    <cacheField name="Order_ID" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="2001" maxValue="2050"/>
+    </cacheField>
+    <cacheField name="Order_Date" numFmtId="0">
+      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2026-02-01T00:00:00" maxDate="2026-03-23T00:00:00"/>
+    </cacheField>
+    <cacheField name="City" numFmtId="0">
+      <sharedItems containsBlank="1" count="5">
+        <s v="Bangalore"/>
+        <s v="Pune"/>
+        <s v="Mumbai"/>
+        <s v="Delhi"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Delivery_Status" numFmtId="0">
+      <sharedItems containsBlank="1" count="4">
+        <s v="Cancelled"/>
+        <s v="Delayed"/>
+        <s v="Delivered"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Delivery_Time_Days" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="9"/>
+    </cacheField>
+    <cacheField name="Product_Type" numFmtId="0">
+      <sharedItems containsBlank="1" count="4">
+        <s v="Groceries"/>
+        <s v="Electronics"/>
+        <s v="Clothing"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Customer_Rating" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="5"/>
+    </cacheField>
+    <cacheField name="Delivery_Partner" numFmtId="0">
+      <sharedItems containsBlank="1" count="4">
+        <s v="DHL"/>
+        <s v="Delhivery"/>
+        <s v="BlueDart"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Payment_Type" numFmtId="0">
+      <sharedItems containsBlank="1" count="4">
+        <s v="Card"/>
+        <s v="Cash"/>
+        <s v="UPI"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Order_Value" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="327" maxValue="4980"/>
+    </cacheField>
+    <cacheField name="Delivery Category" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Rating Category" numFmtId="0">
+      <sharedItems containsBlank="1"/>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -7125,12 +12220,731 @@
 </pivotCacheRecords>
 </file>
 
+<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="51">
+  <r>
+    <n v="2001"/>
+    <d v="2026-02-01T00:00:00"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="2"/>
+    <x v="0"/>
+    <n v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="3527"/>
+    <s v="Fast"/>
+    <s v="Poor"/>
+  </r>
+  <r>
+    <n v="2002"/>
+    <d v="2026-02-02T00:00:00"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="0"/>
+    <n v="2"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="3594"/>
+    <s v="Medium"/>
+    <s v="Poor"/>
+  </r>
+  <r>
+    <n v="2003"/>
+    <d v="2026-02-03T00:00:00"/>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="8"/>
+    <x v="1"/>
+    <n v="4"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="327"/>
+    <s v="Slow"/>
+    <s v="Good"/>
+  </r>
+  <r>
+    <n v="2004"/>
+    <d v="2026-02-04T00:00:00"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="9"/>
+    <x v="0"/>
+    <n v="4"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="2265"/>
+    <s v="Slow"/>
+    <s v="Good"/>
+  </r>
+  <r>
+    <n v="2005"/>
+    <d v="2026-02-05T00:00:00"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="9"/>
+    <x v="0"/>
+    <n v="2"/>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="2016"/>
+    <s v="Slow"/>
+    <s v="Poor"/>
+  </r>
+  <r>
+    <n v="2006"/>
+    <d v="2026-02-06T00:00:00"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="1"/>
+    <x v="1"/>
+    <n v="3"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="769"/>
+    <s v="Fast"/>
+    <s v="Average"/>
+  </r>
+  <r>
+    <n v="2007"/>
+    <d v="2026-02-07T00:00:00"/>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="9"/>
+    <x v="1"/>
+    <n v="1"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="2095"/>
+    <s v="Slow"/>
+    <s v="Poor"/>
+  </r>
+  <r>
+    <n v="2008"/>
+    <d v="2026-02-08T00:00:00"/>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="7"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="2933"/>
+    <s v="Slow"/>
+    <s v="Good"/>
+  </r>
+  <r>
+    <n v="2009"/>
+    <d v="2026-02-09T00:00:00"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="9"/>
+    <x v="0"/>
+    <n v="1"/>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="4063"/>
+    <s v="Slow"/>
+    <s v="Poor"/>
+  </r>
+  <r>
+    <n v="2010"/>
+    <d v="2026-02-10T00:00:00"/>
+    <x v="3"/>
+    <x v="2"/>
+    <n v="8"/>
+    <x v="0"/>
+    <n v="1"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="4921"/>
+    <s v="Slow"/>
+    <s v="Poor"/>
+  </r>
+  <r>
+    <n v="2011"/>
+    <d v="2026-02-11T00:00:00"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="2"/>
+    <n v="3"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="4214"/>
+    <s v="Fast"/>
+    <s v="Average"/>
+  </r>
+  <r>
+    <n v="2012"/>
+    <d v="2026-02-12T00:00:00"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="8"/>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="3101"/>
+    <s v="Slow"/>
+    <s v="Poor"/>
+  </r>
+  <r>
+    <n v="2013"/>
+    <d v="2026-02-13T00:00:00"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="8"/>
+    <x v="2"/>
+    <n v="2"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="1886"/>
+    <s v="Slow"/>
+    <s v="Poor"/>
+  </r>
+  <r>
+    <n v="2014"/>
+    <d v="2026-02-14T00:00:00"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="3"/>
+    <x v="1"/>
+    <n v="2"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="3209"/>
+    <s v="Fast"/>
+    <s v="Poor"/>
+  </r>
+  <r>
+    <n v="2015"/>
+    <d v="2026-02-15T00:00:00"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="1"/>
+    <x v="2"/>
+    <n v="4"/>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="354"/>
+    <s v="Fast"/>
+    <s v="Good"/>
+  </r>
+  <r>
+    <n v="2016"/>
+    <d v="2026-02-16T00:00:00"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="8"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="2737"/>
+    <s v="Slow"/>
+    <s v="Good"/>
+  </r>
+  <r>
+    <n v="2017"/>
+    <d v="2026-02-17T00:00:00"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="3"/>
+    <x v="1"/>
+    <n v="1"/>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="1609"/>
+    <s v="Fast"/>
+    <s v="Poor"/>
+  </r>
+  <r>
+    <n v="2018"/>
+    <d v="2026-02-18T00:00:00"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3"/>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="4257"/>
+    <s v="Fast"/>
+    <s v="Poor"/>
+  </r>
+  <r>
+    <n v="2019"/>
+    <d v="2026-02-19T00:00:00"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="1"/>
+    <x v="2"/>
+    <n v="3"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="984"/>
+    <s v="Fast"/>
+    <s v="Average"/>
+  </r>
+  <r>
+    <n v="2020"/>
+    <d v="2026-02-20T00:00:00"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="5"/>
+    <x v="2"/>
+    <n v="2"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="3375"/>
+    <s v="Medium"/>
+    <s v="Poor"/>
+  </r>
+  <r>
+    <n v="2021"/>
+    <d v="2026-02-21T00:00:00"/>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="7"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="4541"/>
+    <s v="Slow"/>
+    <s v="Good"/>
+  </r>
+  <r>
+    <n v="2022"/>
+    <d v="2026-02-22T00:00:00"/>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="9"/>
+    <x v="2"/>
+    <n v="4"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="3006"/>
+    <s v="Slow"/>
+    <s v="Good"/>
+  </r>
+  <r>
+    <n v="2023"/>
+    <d v="2026-02-23T00:00:00"/>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="7"/>
+    <x v="0"/>
+    <n v="2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="737"/>
+    <s v="Slow"/>
+    <s v="Poor"/>
+  </r>
+  <r>
+    <n v="2024"/>
+    <d v="2026-02-24T00:00:00"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="9"/>
+    <x v="1"/>
+    <n v="4"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="2041"/>
+    <s v="Slow"/>
+    <s v="Good"/>
+  </r>
+  <r>
+    <n v="2025"/>
+    <d v="2026-02-25T00:00:00"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="8"/>
+    <x v="0"/>
+    <n v="3"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="2655"/>
+    <s v="Slow"/>
+    <s v="Average"/>
+  </r>
+  <r>
+    <n v="2026"/>
+    <d v="2026-02-26T00:00:00"/>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="2"/>
+    <x v="2"/>
+    <n v="3"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="724"/>
+    <s v="Fast"/>
+    <s v="Average"/>
+  </r>
+  <r>
+    <n v="2027"/>
+    <d v="2026-02-27T00:00:00"/>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="1"/>
+    <x v="1"/>
+    <n v="1"/>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="3150"/>
+    <s v="Fast"/>
+    <s v="Poor"/>
+  </r>
+  <r>
+    <n v="2028"/>
+    <d v="2026-02-28T00:00:00"/>
+    <x v="3"/>
+    <x v="2"/>
+    <n v="7"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="4331"/>
+    <s v="Slow"/>
+    <s v="Good"/>
+  </r>
+  <r>
+    <n v="2029"/>
+    <d v="2026-03-01T00:00:00"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="7"/>
+    <x v="1"/>
+    <n v="4"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="4980"/>
+    <s v="Slow"/>
+    <s v="Good"/>
+  </r>
+  <r>
+    <n v="2030"/>
+    <d v="2026-03-02T00:00:00"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="8"/>
+    <x v="0"/>
+    <n v="2"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="4315"/>
+    <s v="Slow"/>
+    <s v="Poor"/>
+  </r>
+  <r>
+    <n v="2031"/>
+    <d v="2026-03-03T00:00:00"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="2"/>
+    <n v="3"/>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="2568"/>
+    <s v="Medium"/>
+    <s v="Average"/>
+  </r>
+  <r>
+    <n v="2032"/>
+    <d v="2026-03-04T00:00:00"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="3"/>
+    <x v="1"/>
+    <n v="1"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="4047"/>
+    <s v="Fast"/>
+    <s v="Poor"/>
+  </r>
+  <r>
+    <n v="2033"/>
+    <d v="2026-03-05T00:00:00"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="8"/>
+    <x v="1"/>
+    <n v="1"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="4695"/>
+    <s v="Slow"/>
+    <s v="Poor"/>
+  </r>
+  <r>
+    <n v="2034"/>
+    <d v="2026-03-06T00:00:00"/>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="6"/>
+    <x v="1"/>
+    <n v="4"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="2901"/>
+    <s v="Medium"/>
+    <s v="Good"/>
+  </r>
+  <r>
+    <n v="2035"/>
+    <d v="2026-03-07T00:00:00"/>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="3"/>
+    <x v="0"/>
+    <n v="3"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="1171"/>
+    <s v="Fast"/>
+    <s v="Average"/>
+  </r>
+  <r>
+    <n v="2036"/>
+    <d v="2026-03-08T00:00:00"/>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="1366"/>
+    <s v="Fast"/>
+    <s v="Good"/>
+  </r>
+  <r>
+    <n v="2037"/>
+    <d v="2026-03-09T00:00:00"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="3"/>
+    <x v="2"/>
+    <n v="3"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="2974"/>
+    <s v="Fast"/>
+    <s v="Average"/>
+  </r>
+  <r>
+    <n v="2038"/>
+    <d v="2026-03-10T00:00:00"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="0"/>
+    <n v="4"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="2182"/>
+    <s v="Medium"/>
+    <s v="Good"/>
+  </r>
+  <r>
+    <n v="2039"/>
+    <d v="2026-03-11T00:00:00"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="3"/>
+    <x v="1"/>
+    <n v="4"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="1053"/>
+    <s v="Fast"/>
+    <s v="Good"/>
+  </r>
+  <r>
+    <n v="2040"/>
+    <d v="2026-03-12T00:00:00"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="1"/>
+    <x v="2"/>
+    <n v="3"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="4346"/>
+    <s v="Fast"/>
+    <s v="Average"/>
+  </r>
+  <r>
+    <n v="2041"/>
+    <d v="2026-03-13T00:00:00"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="1"/>
+    <n v="4"/>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="3936"/>
+    <s v="Medium"/>
+    <s v="Good"/>
+  </r>
+  <r>
+    <n v="2042"/>
+    <d v="2026-03-14T00:00:00"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="7"/>
+    <x v="1"/>
+    <n v="3"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="3969"/>
+    <s v="Slow"/>
+    <s v="Average"/>
+  </r>
+  <r>
+    <n v="2043"/>
+    <d v="2026-03-15T00:00:00"/>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="7"/>
+    <x v="0"/>
+    <n v="2"/>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="774"/>
+    <s v="Slow"/>
+    <s v="Poor"/>
+  </r>
+  <r>
+    <n v="2044"/>
+    <d v="2026-03-16T00:00:00"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="9"/>
+    <x v="2"/>
+    <n v="3"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="3461"/>
+    <s v="Slow"/>
+    <s v="Average"/>
+  </r>
+  <r>
+    <n v="2045"/>
+    <d v="2026-03-17T00:00:00"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="3"/>
+    <x v="0"/>
+    <n v="3"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="1348"/>
+    <s v="Fast"/>
+    <s v="Average"/>
+  </r>
+  <r>
+    <n v="2046"/>
+    <d v="2026-03-18T00:00:00"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="7"/>
+    <x v="0"/>
+    <n v="4"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1915"/>
+    <s v="Slow"/>
+    <s v="Good"/>
+  </r>
+  <r>
+    <n v="2047"/>
+    <d v="2026-03-19T00:00:00"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="1"/>
+    <x v="2"/>
+    <n v="4"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="4977"/>
+    <s v="Fast"/>
+    <s v="Good"/>
+  </r>
+  <r>
+    <n v="2048"/>
+    <d v="2026-03-20T00:00:00"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="4"/>
+    <x v="1"/>
+    <n v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="4054"/>
+    <s v="Medium"/>
+    <s v="Poor"/>
+  </r>
+  <r>
+    <n v="2049"/>
+    <d v="2026-03-21T00:00:00"/>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="4"/>
+    <x v="1"/>
+    <n v="1"/>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="2691"/>
+    <s v="Medium"/>
+    <s v="Poor"/>
+  </r>
+  <r>
+    <n v="2050"/>
+    <d v="2026-03-22T00:00:00"/>
+    <x v="3"/>
+    <x v="2"/>
+    <n v="5"/>
+    <x v="2"/>
+    <n v="2"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="2860"/>
+    <s v="Medium"/>
+    <s v="Poor"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <x v="4"/>
+    <x v="3"/>
+    <m/>
+    <x v="3"/>
+    <m/>
+    <x v="3"/>
+    <x v="3"/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+</pivotCacheRecords>
+</file>
+
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C93E735D-913B-41CF-99AA-DD8855596038}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14">
-  <location ref="J4:K7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A5767127-8E9A-41B0-BEFE-2CB22CA70E3D}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+  <location ref="G4:H8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField dataField="1" showAll="0"/>
-    <pivotField axis="axisRow" numFmtId="14" showAll="0">
+    <pivotField numFmtId="14" showAll="0">
       <items count="51">
         <item x="0"/>
         <item x="1"/>
@@ -7194,7 +13008,7 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0">
+    <pivotField axis="axisRow" showAll="0">
       <items count="4">
         <item x="0"/>
         <item x="1"/>
@@ -7202,554 +13016,6 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="369">
-        <item sd="0" x="0"/>
-        <item sd="0" x="1"/>
-        <item sd="0" x="2"/>
-        <item sd="0" x="3"/>
-        <item sd="0" x="4"/>
-        <item sd="0" x="5"/>
-        <item sd="0" x="6"/>
-        <item sd="0" x="7"/>
-        <item sd="0" x="8"/>
-        <item sd="0" x="9"/>
-        <item sd="0" x="10"/>
-        <item sd="0" x="11"/>
-        <item sd="0" x="12"/>
-        <item sd="0" x="13"/>
-        <item sd="0" x="14"/>
-        <item sd="0" x="15"/>
-        <item sd="0" x="16"/>
-        <item sd="0" x="17"/>
-        <item sd="0" x="18"/>
-        <item sd="0" x="19"/>
-        <item sd="0" x="20"/>
-        <item sd="0" x="21"/>
-        <item sd="0" x="22"/>
-        <item sd="0" x="23"/>
-        <item sd="0" x="24"/>
-        <item sd="0" x="25"/>
-        <item sd="0" x="26"/>
-        <item sd="0" x="27"/>
-        <item sd="0" x="28"/>
-        <item sd="0" x="29"/>
-        <item sd="0" x="30"/>
-        <item sd="0" x="31"/>
-        <item sd="0" x="32"/>
-        <item sd="0" x="33"/>
-        <item sd="0" x="34"/>
-        <item sd="0" x="35"/>
-        <item sd="0" x="36"/>
-        <item sd="0" x="37"/>
-        <item sd="0" x="38"/>
-        <item sd="0" x="39"/>
-        <item sd="0" x="40"/>
-        <item sd="0" x="41"/>
-        <item sd="0" x="42"/>
-        <item sd="0" x="43"/>
-        <item sd="0" x="44"/>
-        <item sd="0" x="45"/>
-        <item sd="0" x="46"/>
-        <item sd="0" x="47"/>
-        <item sd="0" x="48"/>
-        <item sd="0" x="49"/>
-        <item sd="0" x="50"/>
-        <item sd="0" x="51"/>
-        <item sd="0" x="52"/>
-        <item sd="0" x="53"/>
-        <item sd="0" x="54"/>
-        <item sd="0" x="55"/>
-        <item sd="0" x="56"/>
-        <item sd="0" x="57"/>
-        <item sd="0" x="58"/>
-        <item sd="0" x="59"/>
-        <item sd="0" x="60"/>
-        <item sd="0" x="61"/>
-        <item sd="0" x="62"/>
-        <item sd="0" x="63"/>
-        <item sd="0" x="64"/>
-        <item sd="0" x="65"/>
-        <item sd="0" x="66"/>
-        <item sd="0" x="67"/>
-        <item sd="0" x="68"/>
-        <item sd="0" x="69"/>
-        <item sd="0" x="70"/>
-        <item sd="0" x="71"/>
-        <item sd="0" x="72"/>
-        <item sd="0" x="73"/>
-        <item sd="0" x="74"/>
-        <item sd="0" x="75"/>
-        <item sd="0" x="76"/>
-        <item sd="0" x="77"/>
-        <item sd="0" x="78"/>
-        <item sd="0" x="79"/>
-        <item sd="0" x="80"/>
-        <item sd="0" x="81"/>
-        <item sd="0" x="82"/>
-        <item sd="0" x="83"/>
-        <item sd="0" x="84"/>
-        <item sd="0" x="85"/>
-        <item sd="0" x="86"/>
-        <item sd="0" x="87"/>
-        <item sd="0" x="88"/>
-        <item sd="0" x="89"/>
-        <item sd="0" x="90"/>
-        <item sd="0" x="91"/>
-        <item sd="0" x="92"/>
-        <item sd="0" x="93"/>
-        <item sd="0" x="94"/>
-        <item sd="0" x="95"/>
-        <item sd="0" x="96"/>
-        <item sd="0" x="97"/>
-        <item sd="0" x="98"/>
-        <item sd="0" x="99"/>
-        <item sd="0" x="100"/>
-        <item sd="0" x="101"/>
-        <item sd="0" x="102"/>
-        <item sd="0" x="103"/>
-        <item sd="0" x="104"/>
-        <item sd="0" x="105"/>
-        <item sd="0" x="106"/>
-        <item sd="0" x="107"/>
-        <item sd="0" x="108"/>
-        <item sd="0" x="109"/>
-        <item sd="0" x="110"/>
-        <item sd="0" x="111"/>
-        <item sd="0" x="112"/>
-        <item sd="0" x="113"/>
-        <item sd="0" x="114"/>
-        <item sd="0" x="115"/>
-        <item sd="0" x="116"/>
-        <item sd="0" x="117"/>
-        <item sd="0" x="118"/>
-        <item sd="0" x="119"/>
-        <item sd="0" x="120"/>
-        <item sd="0" x="121"/>
-        <item sd="0" x="122"/>
-        <item sd="0" x="123"/>
-        <item sd="0" x="124"/>
-        <item sd="0" x="125"/>
-        <item sd="0" x="126"/>
-        <item sd="0" x="127"/>
-        <item sd="0" x="128"/>
-        <item sd="0" x="129"/>
-        <item sd="0" x="130"/>
-        <item sd="0" x="131"/>
-        <item sd="0" x="132"/>
-        <item sd="0" x="133"/>
-        <item sd="0" x="134"/>
-        <item sd="0" x="135"/>
-        <item sd="0" x="136"/>
-        <item sd="0" x="137"/>
-        <item sd="0" x="138"/>
-        <item sd="0" x="139"/>
-        <item sd="0" x="140"/>
-        <item sd="0" x="141"/>
-        <item sd="0" x="142"/>
-        <item sd="0" x="143"/>
-        <item sd="0" x="144"/>
-        <item sd="0" x="145"/>
-        <item sd="0" x="146"/>
-        <item sd="0" x="147"/>
-        <item sd="0" x="148"/>
-        <item sd="0" x="149"/>
-        <item sd="0" x="150"/>
-        <item sd="0" x="151"/>
-        <item sd="0" x="152"/>
-        <item sd="0" x="153"/>
-        <item sd="0" x="154"/>
-        <item sd="0" x="155"/>
-        <item sd="0" x="156"/>
-        <item sd="0" x="157"/>
-        <item sd="0" x="158"/>
-        <item sd="0" x="159"/>
-        <item sd="0" x="160"/>
-        <item sd="0" x="161"/>
-        <item sd="0" x="162"/>
-        <item sd="0" x="163"/>
-        <item sd="0" x="164"/>
-        <item sd="0" x="165"/>
-        <item sd="0" x="166"/>
-        <item sd="0" x="167"/>
-        <item sd="0" x="168"/>
-        <item sd="0" x="169"/>
-        <item sd="0" x="170"/>
-        <item sd="0" x="171"/>
-        <item sd="0" x="172"/>
-        <item sd="0" x="173"/>
-        <item sd="0" x="174"/>
-        <item sd="0" x="175"/>
-        <item sd="0" x="176"/>
-        <item sd="0" x="177"/>
-        <item sd="0" x="178"/>
-        <item sd="0" x="179"/>
-        <item sd="0" x="180"/>
-        <item sd="0" x="181"/>
-        <item sd="0" x="182"/>
-        <item sd="0" x="183"/>
-        <item sd="0" x="184"/>
-        <item sd="0" x="185"/>
-        <item sd="0" x="186"/>
-        <item sd="0" x="187"/>
-        <item sd="0" x="188"/>
-        <item sd="0" x="189"/>
-        <item sd="0" x="190"/>
-        <item sd="0" x="191"/>
-        <item sd="0" x="192"/>
-        <item sd="0" x="193"/>
-        <item sd="0" x="194"/>
-        <item sd="0" x="195"/>
-        <item sd="0" x="196"/>
-        <item sd="0" x="197"/>
-        <item sd="0" x="198"/>
-        <item sd="0" x="199"/>
-        <item sd="0" x="200"/>
-        <item sd="0" x="201"/>
-        <item sd="0" x="202"/>
-        <item sd="0" x="203"/>
-        <item sd="0" x="204"/>
-        <item sd="0" x="205"/>
-        <item sd="0" x="206"/>
-        <item sd="0" x="207"/>
-        <item sd="0" x="208"/>
-        <item sd="0" x="209"/>
-        <item sd="0" x="210"/>
-        <item sd="0" x="211"/>
-        <item sd="0" x="212"/>
-        <item sd="0" x="213"/>
-        <item sd="0" x="214"/>
-        <item sd="0" x="215"/>
-        <item sd="0" x="216"/>
-        <item sd="0" x="217"/>
-        <item sd="0" x="218"/>
-        <item sd="0" x="219"/>
-        <item sd="0" x="220"/>
-        <item sd="0" x="221"/>
-        <item sd="0" x="222"/>
-        <item sd="0" x="223"/>
-        <item sd="0" x="224"/>
-        <item sd="0" x="225"/>
-        <item sd="0" x="226"/>
-        <item sd="0" x="227"/>
-        <item sd="0" x="228"/>
-        <item sd="0" x="229"/>
-        <item sd="0" x="230"/>
-        <item sd="0" x="231"/>
-        <item sd="0" x="232"/>
-        <item sd="0" x="233"/>
-        <item sd="0" x="234"/>
-        <item sd="0" x="235"/>
-        <item sd="0" x="236"/>
-        <item sd="0" x="237"/>
-        <item sd="0" x="238"/>
-        <item sd="0" x="239"/>
-        <item sd="0" x="240"/>
-        <item sd="0" x="241"/>
-        <item sd="0" x="242"/>
-        <item sd="0" x="243"/>
-        <item sd="0" x="244"/>
-        <item sd="0" x="245"/>
-        <item sd="0" x="246"/>
-        <item sd="0" x="247"/>
-        <item sd="0" x="248"/>
-        <item sd="0" x="249"/>
-        <item sd="0" x="250"/>
-        <item sd="0" x="251"/>
-        <item sd="0" x="252"/>
-        <item sd="0" x="253"/>
-        <item sd="0" x="254"/>
-        <item sd="0" x="255"/>
-        <item sd="0" x="256"/>
-        <item sd="0" x="257"/>
-        <item sd="0" x="258"/>
-        <item sd="0" x="259"/>
-        <item sd="0" x="260"/>
-        <item sd="0" x="261"/>
-        <item sd="0" x="262"/>
-        <item sd="0" x="263"/>
-        <item sd="0" x="264"/>
-        <item sd="0" x="265"/>
-        <item sd="0" x="266"/>
-        <item sd="0" x="267"/>
-        <item sd="0" x="268"/>
-        <item sd="0" x="269"/>
-        <item sd="0" x="270"/>
-        <item sd="0" x="271"/>
-        <item sd="0" x="272"/>
-        <item sd="0" x="273"/>
-        <item sd="0" x="274"/>
-        <item sd="0" x="275"/>
-        <item sd="0" x="276"/>
-        <item sd="0" x="277"/>
-        <item sd="0" x="278"/>
-        <item sd="0" x="279"/>
-        <item sd="0" x="280"/>
-        <item sd="0" x="281"/>
-        <item sd="0" x="282"/>
-        <item sd="0" x="283"/>
-        <item sd="0" x="284"/>
-        <item sd="0" x="285"/>
-        <item sd="0" x="286"/>
-        <item sd="0" x="287"/>
-        <item sd="0" x="288"/>
-        <item sd="0" x="289"/>
-        <item sd="0" x="290"/>
-        <item sd="0" x="291"/>
-        <item sd="0" x="292"/>
-        <item sd="0" x="293"/>
-        <item sd="0" x="294"/>
-        <item sd="0" x="295"/>
-        <item sd="0" x="296"/>
-        <item sd="0" x="297"/>
-        <item sd="0" x="298"/>
-        <item sd="0" x="299"/>
-        <item sd="0" x="300"/>
-        <item sd="0" x="301"/>
-        <item sd="0" x="302"/>
-        <item sd="0" x="303"/>
-        <item sd="0" x="304"/>
-        <item sd="0" x="305"/>
-        <item sd="0" x="306"/>
-        <item sd="0" x="307"/>
-        <item sd="0" x="308"/>
-        <item sd="0" x="309"/>
-        <item sd="0" x="310"/>
-        <item sd="0" x="311"/>
-        <item sd="0" x="312"/>
-        <item sd="0" x="313"/>
-        <item sd="0" x="314"/>
-        <item sd="0" x="315"/>
-        <item sd="0" x="316"/>
-        <item sd="0" x="317"/>
-        <item sd="0" x="318"/>
-        <item sd="0" x="319"/>
-        <item sd="0" x="320"/>
-        <item sd="0" x="321"/>
-        <item sd="0" x="322"/>
-        <item sd="0" x="323"/>
-        <item sd="0" x="324"/>
-        <item sd="0" x="325"/>
-        <item sd="0" x="326"/>
-        <item sd="0" x="327"/>
-        <item sd="0" x="328"/>
-        <item sd="0" x="329"/>
-        <item sd="0" x="330"/>
-        <item sd="0" x="331"/>
-        <item sd="0" x="332"/>
-        <item sd="0" x="333"/>
-        <item sd="0" x="334"/>
-        <item sd="0" x="335"/>
-        <item sd="0" x="336"/>
-        <item sd="0" x="337"/>
-        <item sd="0" x="338"/>
-        <item sd="0" x="339"/>
-        <item sd="0" x="340"/>
-        <item sd="0" x="341"/>
-        <item sd="0" x="342"/>
-        <item sd="0" x="343"/>
-        <item sd="0" x="344"/>
-        <item sd="0" x="345"/>
-        <item sd="0" x="346"/>
-        <item sd="0" x="347"/>
-        <item sd="0" x="348"/>
-        <item sd="0" x="349"/>
-        <item sd="0" x="350"/>
-        <item sd="0" x="351"/>
-        <item sd="0" x="352"/>
-        <item sd="0" x="353"/>
-        <item sd="0" x="354"/>
-        <item sd="0" x="355"/>
-        <item sd="0" x="356"/>
-        <item sd="0" x="357"/>
-        <item sd="0" x="358"/>
-        <item sd="0" x="359"/>
-        <item sd="0" x="360"/>
-        <item sd="0" x="361"/>
-        <item sd="0" x="362"/>
-        <item sd="0" x="363"/>
-        <item sd="0" x="364"/>
-        <item sd="0" x="365"/>
-        <item sd="0" x="366"/>
-        <item sd="0" x="367"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="15">
-        <item sd="0" x="0"/>
-        <item sd="0" x="1"/>
-        <item sd="0" x="2"/>
-        <item sd="0" x="3"/>
-        <item sd="0" x="4"/>
-        <item sd="0" x="5"/>
-        <item sd="0" x="6"/>
-        <item sd="0" x="7"/>
-        <item sd="0" x="8"/>
-        <item sd="0" x="9"/>
-        <item sd="0" x="10"/>
-        <item sd="0" x="11"/>
-        <item sd="0" x="12"/>
-        <item sd="0" x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="3">
-    <field x="13"/>
-    <field x="12"/>
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Order_ID" fld="0" subtotal="count" baseField="7" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="2">
-    <chartFormat chart="9" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="13" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A1D670F7-E3BD-484D-9DB9-F0E601AE9F93}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
-  <location ref="D3:E8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="14">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="51">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -8152,7 +13418,131 @@
     </pivotField>
   </pivotFields>
   <rowFields count="1">
-    <field x="2"/>
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Order_ID" fld="0" subtotal="count" baseField="2" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="4">
+    <chartFormat chart="1" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7205A76B-00A9-4A43-B7F6-C3ADC33D1A08}" name="PivotTable6" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+  <location ref="D12:E17" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0" sortType="ascending">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="8"/>
   </rowFields>
   <rowItems count="5">
     <i>
@@ -8175,7 +13565,7 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Count of Order_ID" fld="0" subtotal="count" baseField="2" baseItem="0"/>
+    <dataField name="Count of Order_ID" fld="0" subtotal="count" baseField="8" baseItem="0"/>
   </dataFields>
   <chartFormats count="1">
     <chartFormat chart="1" format="0" series="1">
@@ -8200,7 +13590,264 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1A6E4B2C-7E6E-4088-BC40-8BB377F49347}" name="PivotTable5" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+  <location ref="H3:I8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Delivery_Time_Days" fld="4" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="3" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1E261570-D8E8-4D15-A92E-CADE9EE5161C}" name="PivotTable4" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
+  <location ref="E3:F9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Order_Value" fld="9" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="8" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable13.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5C3287BF-851E-4A55-91F1-36D58F444532}" name="PivotTable3" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0" sortType="ascending">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="7"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Customer_Rating" fld="6" subtotal="average" baseField="7" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1CA8C763-BDDF-47C2-8DF6-3E6581E20ACE}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
   <location ref="A3:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
@@ -8746,7 +14393,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F95D96F4-63DB-476D-9483-9149BFF7148B}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="H14:I20" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
@@ -9359,7 +15006,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6443F01F-58BC-4109-A56A-81B5E9803008}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="20">
   <location ref="D13:F17" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
@@ -9915,7 +15562,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D068C8B3-B2BA-4FDE-84C4-70C16CB67EE6}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A12:B16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
@@ -10435,12 +16082,12 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A5767127-8E9A-41B0-BEFE-2CB22CA70E3D}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
-  <location ref="G4:H8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C93E735D-913B-41CF-99AA-DD8855596038}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14">
+  <location ref="J4:K7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField dataField="1" showAll="0"/>
-    <pivotField numFmtId="14" showAll="0">
+    <pivotField axis="axisRow" numFmtId="14" showAll="0">
       <items count="51">
         <item x="0"/>
         <item x="1"/>
@@ -10504,7 +16151,7 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField axis="axisRow" showAll="0">
+    <pivotField showAll="0">
       <items count="4">
         <item x="0"/>
         <item x="1"/>
@@ -10512,6 +16159,554 @@
         <item t="default"/>
       </items>
     </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="369">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item sd="0" x="14"/>
+        <item sd="0" x="15"/>
+        <item sd="0" x="16"/>
+        <item sd="0" x="17"/>
+        <item sd="0" x="18"/>
+        <item sd="0" x="19"/>
+        <item sd="0" x="20"/>
+        <item sd="0" x="21"/>
+        <item sd="0" x="22"/>
+        <item sd="0" x="23"/>
+        <item sd="0" x="24"/>
+        <item sd="0" x="25"/>
+        <item sd="0" x="26"/>
+        <item sd="0" x="27"/>
+        <item sd="0" x="28"/>
+        <item sd="0" x="29"/>
+        <item sd="0" x="30"/>
+        <item sd="0" x="31"/>
+        <item sd="0" x="32"/>
+        <item sd="0" x="33"/>
+        <item sd="0" x="34"/>
+        <item sd="0" x="35"/>
+        <item sd="0" x="36"/>
+        <item sd="0" x="37"/>
+        <item sd="0" x="38"/>
+        <item sd="0" x="39"/>
+        <item sd="0" x="40"/>
+        <item sd="0" x="41"/>
+        <item sd="0" x="42"/>
+        <item sd="0" x="43"/>
+        <item sd="0" x="44"/>
+        <item sd="0" x="45"/>
+        <item sd="0" x="46"/>
+        <item sd="0" x="47"/>
+        <item sd="0" x="48"/>
+        <item sd="0" x="49"/>
+        <item sd="0" x="50"/>
+        <item sd="0" x="51"/>
+        <item sd="0" x="52"/>
+        <item sd="0" x="53"/>
+        <item sd="0" x="54"/>
+        <item sd="0" x="55"/>
+        <item sd="0" x="56"/>
+        <item sd="0" x="57"/>
+        <item sd="0" x="58"/>
+        <item sd="0" x="59"/>
+        <item sd="0" x="60"/>
+        <item sd="0" x="61"/>
+        <item sd="0" x="62"/>
+        <item sd="0" x="63"/>
+        <item sd="0" x="64"/>
+        <item sd="0" x="65"/>
+        <item sd="0" x="66"/>
+        <item sd="0" x="67"/>
+        <item sd="0" x="68"/>
+        <item sd="0" x="69"/>
+        <item sd="0" x="70"/>
+        <item sd="0" x="71"/>
+        <item sd="0" x="72"/>
+        <item sd="0" x="73"/>
+        <item sd="0" x="74"/>
+        <item sd="0" x="75"/>
+        <item sd="0" x="76"/>
+        <item sd="0" x="77"/>
+        <item sd="0" x="78"/>
+        <item sd="0" x="79"/>
+        <item sd="0" x="80"/>
+        <item sd="0" x="81"/>
+        <item sd="0" x="82"/>
+        <item sd="0" x="83"/>
+        <item sd="0" x="84"/>
+        <item sd="0" x="85"/>
+        <item sd="0" x="86"/>
+        <item sd="0" x="87"/>
+        <item sd="0" x="88"/>
+        <item sd="0" x="89"/>
+        <item sd="0" x="90"/>
+        <item sd="0" x="91"/>
+        <item sd="0" x="92"/>
+        <item sd="0" x="93"/>
+        <item sd="0" x="94"/>
+        <item sd="0" x="95"/>
+        <item sd="0" x="96"/>
+        <item sd="0" x="97"/>
+        <item sd="0" x="98"/>
+        <item sd="0" x="99"/>
+        <item sd="0" x="100"/>
+        <item sd="0" x="101"/>
+        <item sd="0" x="102"/>
+        <item sd="0" x="103"/>
+        <item sd="0" x="104"/>
+        <item sd="0" x="105"/>
+        <item sd="0" x="106"/>
+        <item sd="0" x="107"/>
+        <item sd="0" x="108"/>
+        <item sd="0" x="109"/>
+        <item sd="0" x="110"/>
+        <item sd="0" x="111"/>
+        <item sd="0" x="112"/>
+        <item sd="0" x="113"/>
+        <item sd="0" x="114"/>
+        <item sd="0" x="115"/>
+        <item sd="0" x="116"/>
+        <item sd="0" x="117"/>
+        <item sd="0" x="118"/>
+        <item sd="0" x="119"/>
+        <item sd="0" x="120"/>
+        <item sd="0" x="121"/>
+        <item sd="0" x="122"/>
+        <item sd="0" x="123"/>
+        <item sd="0" x="124"/>
+        <item sd="0" x="125"/>
+        <item sd="0" x="126"/>
+        <item sd="0" x="127"/>
+        <item sd="0" x="128"/>
+        <item sd="0" x="129"/>
+        <item sd="0" x="130"/>
+        <item sd="0" x="131"/>
+        <item sd="0" x="132"/>
+        <item sd="0" x="133"/>
+        <item sd="0" x="134"/>
+        <item sd="0" x="135"/>
+        <item sd="0" x="136"/>
+        <item sd="0" x="137"/>
+        <item sd="0" x="138"/>
+        <item sd="0" x="139"/>
+        <item sd="0" x="140"/>
+        <item sd="0" x="141"/>
+        <item sd="0" x="142"/>
+        <item sd="0" x="143"/>
+        <item sd="0" x="144"/>
+        <item sd="0" x="145"/>
+        <item sd="0" x="146"/>
+        <item sd="0" x="147"/>
+        <item sd="0" x="148"/>
+        <item sd="0" x="149"/>
+        <item sd="0" x="150"/>
+        <item sd="0" x="151"/>
+        <item sd="0" x="152"/>
+        <item sd="0" x="153"/>
+        <item sd="0" x="154"/>
+        <item sd="0" x="155"/>
+        <item sd="0" x="156"/>
+        <item sd="0" x="157"/>
+        <item sd="0" x="158"/>
+        <item sd="0" x="159"/>
+        <item sd="0" x="160"/>
+        <item sd="0" x="161"/>
+        <item sd="0" x="162"/>
+        <item sd="0" x="163"/>
+        <item sd="0" x="164"/>
+        <item sd="0" x="165"/>
+        <item sd="0" x="166"/>
+        <item sd="0" x="167"/>
+        <item sd="0" x="168"/>
+        <item sd="0" x="169"/>
+        <item sd="0" x="170"/>
+        <item sd="0" x="171"/>
+        <item sd="0" x="172"/>
+        <item sd="0" x="173"/>
+        <item sd="0" x="174"/>
+        <item sd="0" x="175"/>
+        <item sd="0" x="176"/>
+        <item sd="0" x="177"/>
+        <item sd="0" x="178"/>
+        <item sd="0" x="179"/>
+        <item sd="0" x="180"/>
+        <item sd="0" x="181"/>
+        <item sd="0" x="182"/>
+        <item sd="0" x="183"/>
+        <item sd="0" x="184"/>
+        <item sd="0" x="185"/>
+        <item sd="0" x="186"/>
+        <item sd="0" x="187"/>
+        <item sd="0" x="188"/>
+        <item sd="0" x="189"/>
+        <item sd="0" x="190"/>
+        <item sd="0" x="191"/>
+        <item sd="0" x="192"/>
+        <item sd="0" x="193"/>
+        <item sd="0" x="194"/>
+        <item sd="0" x="195"/>
+        <item sd="0" x="196"/>
+        <item sd="0" x="197"/>
+        <item sd="0" x="198"/>
+        <item sd="0" x="199"/>
+        <item sd="0" x="200"/>
+        <item sd="0" x="201"/>
+        <item sd="0" x="202"/>
+        <item sd="0" x="203"/>
+        <item sd="0" x="204"/>
+        <item sd="0" x="205"/>
+        <item sd="0" x="206"/>
+        <item sd="0" x="207"/>
+        <item sd="0" x="208"/>
+        <item sd="0" x="209"/>
+        <item sd="0" x="210"/>
+        <item sd="0" x="211"/>
+        <item sd="0" x="212"/>
+        <item sd="0" x="213"/>
+        <item sd="0" x="214"/>
+        <item sd="0" x="215"/>
+        <item sd="0" x="216"/>
+        <item sd="0" x="217"/>
+        <item sd="0" x="218"/>
+        <item sd="0" x="219"/>
+        <item sd="0" x="220"/>
+        <item sd="0" x="221"/>
+        <item sd="0" x="222"/>
+        <item sd="0" x="223"/>
+        <item sd="0" x="224"/>
+        <item sd="0" x="225"/>
+        <item sd="0" x="226"/>
+        <item sd="0" x="227"/>
+        <item sd="0" x="228"/>
+        <item sd="0" x="229"/>
+        <item sd="0" x="230"/>
+        <item sd="0" x="231"/>
+        <item sd="0" x="232"/>
+        <item sd="0" x="233"/>
+        <item sd="0" x="234"/>
+        <item sd="0" x="235"/>
+        <item sd="0" x="236"/>
+        <item sd="0" x="237"/>
+        <item sd="0" x="238"/>
+        <item sd="0" x="239"/>
+        <item sd="0" x="240"/>
+        <item sd="0" x="241"/>
+        <item sd="0" x="242"/>
+        <item sd="0" x="243"/>
+        <item sd="0" x="244"/>
+        <item sd="0" x="245"/>
+        <item sd="0" x="246"/>
+        <item sd="0" x="247"/>
+        <item sd="0" x="248"/>
+        <item sd="0" x="249"/>
+        <item sd="0" x="250"/>
+        <item sd="0" x="251"/>
+        <item sd="0" x="252"/>
+        <item sd="0" x="253"/>
+        <item sd="0" x="254"/>
+        <item sd="0" x="255"/>
+        <item sd="0" x="256"/>
+        <item sd="0" x="257"/>
+        <item sd="0" x="258"/>
+        <item sd="0" x="259"/>
+        <item sd="0" x="260"/>
+        <item sd="0" x="261"/>
+        <item sd="0" x="262"/>
+        <item sd="0" x="263"/>
+        <item sd="0" x="264"/>
+        <item sd="0" x="265"/>
+        <item sd="0" x="266"/>
+        <item sd="0" x="267"/>
+        <item sd="0" x="268"/>
+        <item sd="0" x="269"/>
+        <item sd="0" x="270"/>
+        <item sd="0" x="271"/>
+        <item sd="0" x="272"/>
+        <item sd="0" x="273"/>
+        <item sd="0" x="274"/>
+        <item sd="0" x="275"/>
+        <item sd="0" x="276"/>
+        <item sd="0" x="277"/>
+        <item sd="0" x="278"/>
+        <item sd="0" x="279"/>
+        <item sd="0" x="280"/>
+        <item sd="0" x="281"/>
+        <item sd="0" x="282"/>
+        <item sd="0" x="283"/>
+        <item sd="0" x="284"/>
+        <item sd="0" x="285"/>
+        <item sd="0" x="286"/>
+        <item sd="0" x="287"/>
+        <item sd="0" x="288"/>
+        <item sd="0" x="289"/>
+        <item sd="0" x="290"/>
+        <item sd="0" x="291"/>
+        <item sd="0" x="292"/>
+        <item sd="0" x="293"/>
+        <item sd="0" x="294"/>
+        <item sd="0" x="295"/>
+        <item sd="0" x="296"/>
+        <item sd="0" x="297"/>
+        <item sd="0" x="298"/>
+        <item sd="0" x="299"/>
+        <item sd="0" x="300"/>
+        <item sd="0" x="301"/>
+        <item sd="0" x="302"/>
+        <item sd="0" x="303"/>
+        <item sd="0" x="304"/>
+        <item sd="0" x="305"/>
+        <item sd="0" x="306"/>
+        <item sd="0" x="307"/>
+        <item sd="0" x="308"/>
+        <item sd="0" x="309"/>
+        <item sd="0" x="310"/>
+        <item sd="0" x="311"/>
+        <item sd="0" x="312"/>
+        <item sd="0" x="313"/>
+        <item sd="0" x="314"/>
+        <item sd="0" x="315"/>
+        <item sd="0" x="316"/>
+        <item sd="0" x="317"/>
+        <item sd="0" x="318"/>
+        <item sd="0" x="319"/>
+        <item sd="0" x="320"/>
+        <item sd="0" x="321"/>
+        <item sd="0" x="322"/>
+        <item sd="0" x="323"/>
+        <item sd="0" x="324"/>
+        <item sd="0" x="325"/>
+        <item sd="0" x="326"/>
+        <item sd="0" x="327"/>
+        <item sd="0" x="328"/>
+        <item sd="0" x="329"/>
+        <item sd="0" x="330"/>
+        <item sd="0" x="331"/>
+        <item sd="0" x="332"/>
+        <item sd="0" x="333"/>
+        <item sd="0" x="334"/>
+        <item sd="0" x="335"/>
+        <item sd="0" x="336"/>
+        <item sd="0" x="337"/>
+        <item sd="0" x="338"/>
+        <item sd="0" x="339"/>
+        <item sd="0" x="340"/>
+        <item sd="0" x="341"/>
+        <item sd="0" x="342"/>
+        <item sd="0" x="343"/>
+        <item sd="0" x="344"/>
+        <item sd="0" x="345"/>
+        <item sd="0" x="346"/>
+        <item sd="0" x="347"/>
+        <item sd="0" x="348"/>
+        <item sd="0" x="349"/>
+        <item sd="0" x="350"/>
+        <item sd="0" x="351"/>
+        <item sd="0" x="352"/>
+        <item sd="0" x="353"/>
+        <item sd="0" x="354"/>
+        <item sd="0" x="355"/>
+        <item sd="0" x="356"/>
+        <item sd="0" x="357"/>
+        <item sd="0" x="358"/>
+        <item sd="0" x="359"/>
+        <item sd="0" x="360"/>
+        <item sd="0" x="361"/>
+        <item sd="0" x="362"/>
+        <item sd="0" x="363"/>
+        <item sd="0" x="364"/>
+        <item sd="0" x="365"/>
+        <item sd="0" x="366"/>
+        <item sd="0" x="367"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="15">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="3">
+    <field x="13"/>
+    <field x="12"/>
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Order_ID" fld="0" subtotal="count" baseField="7" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="2">
+    <chartFormat chart="9" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="13" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A1D670F7-E3BD-484D-9DB9-F0E601AE9F93}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+  <location ref="D3:E8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="14">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="51">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -10914,9 +17109,9 @@
     </pivotField>
   </pivotFields>
   <rowFields count="1">
-    <field x="3"/>
+    <field x="2"/>
   </rowFields>
-  <rowItems count="4">
+  <rowItems count="5">
     <i>
       <x/>
     </i>
@@ -10925,6 +17120,9 @@
     </i>
     <i>
       <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
     </i>
     <i t="grand">
       <x/>
@@ -10936,7 +17134,7 @@
   <dataFields count="1">
     <dataField name="Count of Order_ID" fld="0" subtotal="count" baseField="2" baseItem="0"/>
   </dataFields>
-  <chartFormats count="4">
+  <chartFormats count="1">
     <chartFormat chart="1" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -10946,38 +17144,208 @@
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="1" format="1">
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8D1A045E-E4C1-44BE-854F-5783FDA7EE0C}" name="PivotTable8" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+  <location ref="A12:B17" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0" sortType="ascending">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="7"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Customer_Rating" fld="6" subtotal="average" baseField="7" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="1" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
+        <references count="1">
           <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="3" count="1" selected="0">
             <x v="0"/>
           </reference>
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="1" format="2">
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{94A9F9ED-97B4-4A4C-85FA-32C9297C4F79}" name="PivotTable7" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+  <location ref="G12:H17" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0" sortType="ascending">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="5"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Order_Value" fld="9" subtotal="average" baseField="5" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="4" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
+        <references count="1">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
-          </reference>
-          <reference field="3" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="1" format="3">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="3" count="1" selected="0">
-            <x v="2"/>
           </reference>
         </references>
       </pivotArea>
@@ -11631,6 +17999,263 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{700E166B-F8C5-4652-B221-34A81E31CF80}">
+  <dimension ref="A3:I17"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5546875" customWidth="1"/>
+    <col min="5" max="5" width="17.109375" customWidth="1"/>
+    <col min="6" max="6" width="20.88671875" customWidth="1"/>
+    <col min="7" max="7" width="18.77734375" customWidth="1"/>
+    <col min="8" max="8" width="24" customWidth="1"/>
+    <col min="9" max="9" width="25.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="4">
+        <v>43961</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="4">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="4">
+        <v>2.8571428571428572</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="4">
+        <v>28801</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="4">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="4">
+        <v>2.95</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="4">
+        <v>22314</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="4">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="E7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="4">
+        <v>44928</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I7" s="4"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="4">
+        <v>2.78</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" s="4"/>
+      <c r="H8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I8" s="4">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="4">
+        <v>140004</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" t="s">
+        <v>31</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="4">
+        <v>16</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H13" s="4">
+        <v>2872.4666666666667</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="4">
+        <v>2.8571428571428572</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="4">
+        <v>21</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H14" s="4">
+        <v>2921.8888888888887</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="4">
+        <v>2.95</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="4">
+        <v>13</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15" s="4">
+        <v>2607.2352941176468</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="4"/>
+      <c r="D16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="4"/>
+      <c r="G16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H16" s="4"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="4">
+        <v>2.78</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" s="4">
+        <v>50</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H17" s="4">
+        <v>2800.08</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId7"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCAB5A01-4880-423E-875F-3BE0C2B6A38A}">
   <dimension ref="A1:L51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
